--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 18,75</t>
+          <t>8,21; 18,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 10,5</t>
+          <t>-0,79; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -1,16</t>
+          <t>-12,36; -1,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 13,08</t>
+          <t>2,92; 12,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,65</t>
+          <t>-2,15; 7,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,29; -14,2</t>
+          <t>-27,28; -13,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,65</t>
+          <t>6,76; 14,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 7,29</t>
+          <t>0,08; 7,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -9,29</t>
+          <t>-18,03; -9,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,29; 43,41</t>
+          <t>16,93; 43,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 24,36</t>
+          <t>-1,51; 23,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,25; -2,77</t>
+          <t>-25,46; -2,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 23,11</t>
+          <t>4,66; 22,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 13,36</t>
+          <t>-3,5; 13,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -24,22</t>
+          <t>-46,33; -23,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 28,82</t>
+          <t>12,42; 28,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 14,5</t>
+          <t>0,15; 14,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -18,29</t>
+          <t>-34,13; -18,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,81</t>
+          <t>2,24; 11,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,17</t>
+          <t>-1,1; 8,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -7,52</t>
+          <t>-33,0; -7,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 11,22</t>
+          <t>2,19; 11,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 5,92</t>
+          <t>-3,0; 5,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -14,4</t>
+          <t>-22,43; -14,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,99</t>
+          <t>3,81; 10,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,71</t>
+          <t>-0,36; 6,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,27; -12,71</t>
+          <t>-30,87; -12,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 27,64</t>
+          <t>4,69; 26,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 19,06</t>
+          <t>-2,37; 18,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,31; -17,0</t>
+          <t>-71,22; -17,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 18,8</t>
+          <t>3,36; 19,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 9,84</t>
+          <t>-4,68; 9,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -24,04</t>
+          <t>-34,89; -23,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 19,46</t>
+          <t>6,95; 19,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,88</t>
+          <t>-0,63; 11,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,07; -23,86</t>
+          <t>-56,66; -23,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 9,53</t>
+          <t>-1,92; 9,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,28</t>
+          <t>-3,59; 7,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; -7,18</t>
+          <t>-18,22; -6,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,95</t>
+          <t>1,07; 10,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,43</t>
+          <t>-6,9; 3,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 12,88</t>
+          <t>-27,69; 14,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,74</t>
+          <t>1,48; 9,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,55</t>
+          <t>-3,76; 3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 8,94</t>
+          <t>-20,64; 7,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 22,55</t>
+          <t>-4,06; 23,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 17,08</t>
+          <t>-7,68; 17,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,04; -16,84</t>
+          <t>-38,27; -16,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 19,13</t>
+          <t>1,75; 18,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 6,03</t>
+          <t>-10,94; 5,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 22,27</t>
+          <t>-45,59; 24,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 17,24</t>
+          <t>2,57; 17,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 7,11</t>
+          <t>-7,07; 7,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 17,17</t>
+          <t>-38,87; 14,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 18,11</t>
+          <t>9,25; 18,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 14,57</t>
+          <t>5,82; 14,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,23; -5,83</t>
+          <t>-14,97; -5,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,83</t>
+          <t>3,37; 11,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,29</t>
+          <t>-3,07; 5,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,37; -18,79</t>
+          <t>-30,61; -18,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,3; 13,82</t>
+          <t>7,39; 13,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,77</t>
+          <t>2,29; 8,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,06; -13,6</t>
+          <t>-21,34; -13,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,2; 45,14</t>
+          <t>21,42; 47,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,9; 36,62</t>
+          <t>13,11; 36,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,63; -14,5</t>
+          <t>-33,92; -13,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 20,87</t>
+          <t>5,51; 20,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 9,45</t>
+          <t>-5,14; 9,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,88; -32,67</t>
+          <t>-50,46; -31,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 28,19</t>
+          <t>14,17; 27,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 17,78</t>
+          <t>4,4; 17,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -27,41</t>
+          <t>-41,84; -27,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,12</t>
+          <t>7,03; 11,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,95</t>
+          <t>2,75; 7,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -8,91</t>
+          <t>-20,14; -8,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,46</t>
+          <t>4,95; 9,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,08</t>
+          <t>-1,39; 3,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -7,55</t>
+          <t>-22,68; -7,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,07</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,94</t>
+          <t>1,43; 4,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -9,31</t>
+          <t>-18,83; -9,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,39; 28,18</t>
+          <t>15,37; 27,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,5</t>
+          <t>5,99; 17,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,66; -20,33</t>
+          <t>-44,75; -20,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,05</t>
+          <t>8,05; 16,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,24</t>
+          <t>-2,23; 5,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; -12,58</t>
+          <t>-37,36; -11,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,61</t>
+          <t>12,4; 19,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,62</t>
+          <t>2,72; 9,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -17,9</t>
+          <t>-35,72; -18,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,07</t>
+          <t>-8,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,96</t>
+          <t>-15,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-11,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 18,66</t>
+          <t>7,57; 18,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 10,01</t>
+          <t>-1,0; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -1,28</t>
+          <t>-13,27; -2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,98</t>
+          <t>2,9; 13,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,84</t>
+          <t>-2,97; 7,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -13,77</t>
+          <t>-20,63; -11,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,29</t>
+          <t>7,34; 14,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,48</t>
+          <t>-0,05; 7,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -9,2</t>
+          <t>-15,12; -8,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,45%</t>
+          <t>-18,11%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,81%</t>
+          <t>-26,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,54%</t>
+          <t>-22,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 43,47</t>
+          <t>15,54; 42,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 23,08</t>
+          <t>-2,18; 23,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,46; -2,6</t>
+          <t>-27,31; -6,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,61</t>
+          <t>4,54; 23,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 13,69</t>
+          <t>-4,84; 13,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,33; -23,81</t>
+          <t>-32,95; -19,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 28,26</t>
+          <t>13,57; 28,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 14,79</t>
+          <t>-0,1; 13,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; -18,14</t>
+          <t>-27,92; -16,23</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-16,76</t>
+          <t>-10,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-18,5</t>
+          <t>-19,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-18,49</t>
+          <t>-14,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,27</t>
+          <t>2,57; 11,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,1</t>
+          <t>-0,78; 8,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,0; -7,81</t>
+          <t>-14,9; -5,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,36</t>
+          <t>2,56; 11,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,88</t>
+          <t>-2,95; 6,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,43; -14,05</t>
+          <t>-23,11; -14,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,16</t>
+          <t>3,48; 9,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,03</t>
+          <t>-0,73; 5,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -12,68</t>
+          <t>-17,54; -11,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-37,01%</t>
+          <t>-23,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-29,71%</t>
+          <t>-30,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,36%</t>
+          <t>-27,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,06</t>
+          <t>5,38; 26,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 18,64</t>
+          <t>-1,59; 20,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,22; -17,54</t>
+          <t>-31,56; -13,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 19,01</t>
+          <t>3,95; 18,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 9,88</t>
+          <t>-4,57; 10,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -23,46</t>
+          <t>-35,48; -24,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 19,79</t>
+          <t>6,36; 18,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,66</t>
+          <t>-1,37; 10,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,66; -23,98</t>
+          <t>-31,82; -22,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-12,83</t>
+          <t>-14,37</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,46</t>
+          <t>-25,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,01</t>
+          <t>-20,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 9,65</t>
+          <t>-1,58; 9,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 7,29</t>
+          <t>-3,8; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -6,81</t>
+          <t>-19,74; -8,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,95</t>
+          <t>1,33; 11,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,14</t>
+          <t>-6,6; 3,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 14,58</t>
+          <t>-30,51; -20,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,01</t>
+          <t>1,28; 8,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,77</t>
+          <t>-3,88; 3,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 7,5</t>
+          <t>-23,76; -16,57</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,6%</t>
+          <t>-32,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-19,04%</t>
+          <t>-43,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-20,94%</t>
+          <t>-38,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 23,08</t>
+          <t>-3,05; 23,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 17,9</t>
+          <t>-8,01; 17,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,27; -16,43</t>
+          <t>-41,19; -20,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 18,99</t>
+          <t>2,1; 19,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 5,43</t>
+          <t>-10,46; 5,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 24,62</t>
+          <t>-49,15; -36,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 17,83</t>
+          <t>2,61; 17,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 7,48</t>
+          <t>-7,08; 7,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 14,26</t>
+          <t>-43,7; -32,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,46</t>
+          <t>-12,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-23,17</t>
+          <t>-21,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-17,05</t>
+          <t>-17,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 18,63</t>
+          <t>9,11; 18,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 14,69</t>
+          <t>6,05; 14,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -5,73</t>
+          <t>-16,67; -7,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 11,81</t>
+          <t>3,33; 11,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,54</t>
+          <t>-3,14; 5,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,61; -18,33</t>
+          <t>-25,44; -17,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 13,62</t>
+          <t>7,46; 13,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,56</t>
+          <t>2,22; 8,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,34; -13,61</t>
+          <t>-20,14; -14,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-24,87%</t>
+          <t>-29,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,08%</t>
+          <t>-36,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-33,36%</t>
+          <t>-33,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,42; 47,06</t>
+          <t>20,17; 45,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,11; 36,33</t>
+          <t>13,69; 37,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -13,92</t>
+          <t>-37,39; -19,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 20,62</t>
+          <t>5,43; 20,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 9,66</t>
+          <t>-5,26; 9,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,46; -31,79</t>
+          <t>-41,62; -31,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,17; 27,76</t>
+          <t>14,08; 28,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 17,31</t>
+          <t>4,23; 17,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,84; -27,62</t>
+          <t>-38,34; -28,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-11,48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-18,24</t>
+          <t>-20,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-15,28</t>
+          <t>-16,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,76</t>
+          <t>6,9; 11,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,73</t>
+          <t>2,69; 7,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -8,9</t>
+          <t>-14,1; -9,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,7</t>
+          <t>4,84; 9,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,13</t>
+          <t>-1,51; 3,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,68; -7,17</t>
+          <t>-22,65; -18,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>6,67; 10,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,7</t>
+          <t>1,39; 4,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -9,65</t>
+          <t>-17,8; -14,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-28,04%</t>
+          <t>-25,87%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,2%</t>
+          <t>-34,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,11%</t>
+          <t>-30,69%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,37; 27,37</t>
+          <t>15,06; 27,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,99</t>
+          <t>5,84; 18,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,75; -20,32</t>
+          <t>-30,82; -21,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,05; 16,51</t>
+          <t>7,81; 16,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,28</t>
+          <t>-2,47; 5,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -11,81</t>
+          <t>-36,92; -31,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,49</t>
+          <t>12,43; 19,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,18</t>
+          <t>2,59; 9,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -18,52</t>
+          <t>-33,44; -27,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
